--- a/Collections/EURO/Latvia/#EURO#Latvia#Regular#[2014-present]#circulation_quality.xlsx
+++ b/Collections/EURO/Latvia/#EURO#Latvia#Regular#[2014-present]#circulation_quality.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\EURO\Latvia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D329587-32A9-47EF-A025-A287EEBE7CB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6F36E92-1C70-4B09-A14D-F206ED728AD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -303,7 +303,6 @@
   <authors>
     <author>Пользователь Windows</author>
     <author>Автор</author>
-    <author>Lord_Alexator</author>
   </authors>
   <commentList>
     <comment ref="E2" authorId="0" shapeId="0" xr:uid="{F9376E3F-F45A-403A-AD6C-FB13DF150052}">
@@ -431,32 +430,6 @@
           </rPr>
           <t>Koninklijke Nederlandse Munt
 (Netherlands mint(Utrecht))</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H8" authorId="2" shapeId="0" xr:uid="{84E0EB3C-77BB-4E65-ABFD-8533AFDC8B78}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t>В наборах BU</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
         </r>
       </text>
     </comment>
@@ -1593,6 +1566,9 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1608,37 +1584,25 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="49" fontId="5" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1649,6 +1613,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1667,1854 +1640,6 @@
   </cellStyles>
   <dxfs count="234">
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3522,6 +1647,1854 @@
     </dxf>
     <dxf>
       <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3554,9 +3527,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="233"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="232" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="231"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="1" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -3839,30 +3812,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="27" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="24"/>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="29"/>
-      <c r="E1" s="30" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="40"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="33" t="s">
+      <c r="F1" s="32"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="41"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="35"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="38"/>
       <c r="M1" s="1"/>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="27"/>
+      <c r="A2" s="28"/>
       <c r="B2" s="24" t="s">
         <v>44</v>
       </c>
@@ -4392,7 +4365,7 @@
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="I3:I6">
-    <cfRule type="containsText" dxfId="230" priority="81" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="233" priority="81" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4409,11 +4382,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7 I10">
-    <cfRule type="containsText" dxfId="229" priority="59" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="232" priority="59" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I7))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I10 I7">
+  <conditionalFormatting sqref="I7 I10">
     <cfRule type="colorScale" priority="60">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4426,7 +4399,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I8">
-    <cfRule type="containsText" dxfId="228" priority="57" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="231" priority="57" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I8))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4443,11 +4416,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9 I11">
-    <cfRule type="containsText" dxfId="227" priority="55" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="230" priority="55" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I9))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I9 I11">
+  <conditionalFormatting sqref="I11 I9">
     <cfRule type="colorScale" priority="56">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4460,7 +4433,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K3:K6">
-    <cfRule type="containsText" dxfId="226" priority="53" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="229" priority="53" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4477,7 +4450,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="containsText" dxfId="225" priority="51" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="228" priority="51" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K7))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4494,11 +4467,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K8 K10">
-    <cfRule type="containsText" dxfId="224" priority="49" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="227" priority="49" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K8))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K10 K8">
+  <conditionalFormatting sqref="K8 K10">
     <cfRule type="colorScale" priority="50">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4511,11 +4484,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K9 K11">
-    <cfRule type="containsText" dxfId="223" priority="47" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="226" priority="47" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K9))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K9 K11">
+  <conditionalFormatting sqref="K11 K9">
     <cfRule type="colorScale" priority="48">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4528,7 +4501,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K9:K11 K3:K6">
-    <cfRule type="containsText" dxfId="222" priority="45" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="225" priority="45" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4545,7 +4518,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K8">
-    <cfRule type="containsText" dxfId="221" priority="43" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="224" priority="43" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K8))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4562,7 +4535,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="containsText" dxfId="220" priority="41" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="223" priority="41" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K7))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4579,7 +4552,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I12">
-    <cfRule type="containsText" dxfId="219" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="222" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I12))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4596,7 +4569,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="containsText" dxfId="218" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="221" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K12))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4613,7 +4586,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="containsText" dxfId="217" priority="35" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="220" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K12))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4630,7 +4603,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J3:J6">
-    <cfRule type="containsText" dxfId="216" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="219" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4647,11 +4620,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7 J10">
-    <cfRule type="containsText" dxfId="215" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="218" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J7))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J10 J7">
+  <conditionalFormatting sqref="J7 J10">
     <cfRule type="colorScale" priority="32">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4664,7 +4637,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J8">
-    <cfRule type="containsText" dxfId="214" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="217" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J8))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4681,11 +4654,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J9 J11">
-    <cfRule type="containsText" dxfId="213" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="216" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J9))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J9 J11">
+  <conditionalFormatting sqref="J11 J9">
     <cfRule type="colorScale" priority="28">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4698,7 +4671,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J12">
-    <cfRule type="containsText" dxfId="212" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="215" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J12))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4715,12 +4688,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L14">
-    <cfRule type="containsText" dxfId="211" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="214" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L14))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I13">
-    <cfRule type="containsText" dxfId="210" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="213" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I13))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4737,7 +4710,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="containsText" dxfId="209" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="212" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K13))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4754,7 +4727,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="containsText" dxfId="208" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="211" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K13))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4771,7 +4744,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J13">
-    <cfRule type="containsText" dxfId="207" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="210" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J13))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4788,7 +4761,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L3:L13">
-    <cfRule type="containsText" dxfId="206" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="209" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4805,7 +4778,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L3:L13">
-    <cfRule type="containsText" dxfId="205" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="208" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4822,7 +4795,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I14">
-    <cfRule type="containsText" dxfId="204" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="207" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I14))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4839,7 +4812,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K14">
-    <cfRule type="containsText" dxfId="203" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="206" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K14))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4856,7 +4829,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K14">
-    <cfRule type="containsText" dxfId="202" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="205" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K14))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4873,7 +4846,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J14">
-    <cfRule type="containsText" dxfId="201" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="204" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J14))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4890,7 +4863,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L14">
-    <cfRule type="containsText" dxfId="200" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="203" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L14))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4940,28 +4913,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="27" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="24"/>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="29"/>
-      <c r="E1" s="30" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="32"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="33" t="s">
+      <c r="F1" s="33"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="34"/>
-      <c r="J1" s="35"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="38"/>
       <c r="K1" s="1"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="27"/>
+      <c r="A2" s="28"/>
       <c r="B2" s="24" t="s">
         <v>44</v>
       </c>
@@ -5012,7 +4985,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="17" t="s">
         <v>0</v>
@@ -5404,7 +5377,7 @@
       </c>
     </row>
     <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="J15" s="39"/>
+      <c r="J15" s="26"/>
     </row>
   </sheetData>
   <autoFilter ref="B2:G2" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
@@ -5416,7 +5389,7 @@
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="H3:H6">
-    <cfRule type="containsText" dxfId="199" priority="143" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="202" priority="143" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5433,7 +5406,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H7 H10:H11">
-    <cfRule type="containsText" dxfId="198" priority="141" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="201" priority="141" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H7))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5450,7 +5423,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H8">
-    <cfRule type="containsText" dxfId="197" priority="139" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="200" priority="139" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H8))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5467,7 +5440,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H9">
-    <cfRule type="containsText" dxfId="196" priority="137" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="199" priority="137" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H9))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5484,7 +5457,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I3:I6">
-    <cfRule type="containsText" dxfId="195" priority="135" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="198" priority="135" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5501,7 +5474,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="containsText" dxfId="194" priority="133" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="197" priority="133" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I7))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5518,11 +5491,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I8 I10">
-    <cfRule type="containsText" dxfId="193" priority="131" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="196" priority="131" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I8))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I8 I10">
+  <conditionalFormatting sqref="I10 I8">
     <cfRule type="colorScale" priority="132">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5535,11 +5508,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9 I11">
-    <cfRule type="containsText" dxfId="192" priority="129" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="195" priority="129" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I9))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I9 I11">
+  <conditionalFormatting sqref="I11 I9">
     <cfRule type="colorScale" priority="130">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5552,7 +5525,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I3:I6 I9:I11">
-    <cfRule type="containsText" dxfId="191" priority="127" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="194" priority="127" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5569,7 +5542,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I8">
-    <cfRule type="containsText" dxfId="190" priority="125" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="193" priority="125" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I8))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5586,7 +5559,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="containsText" dxfId="189" priority="123" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="192" priority="123" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I7))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5603,7 +5576,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="containsText" dxfId="188" priority="121" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="191" priority="121" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H12))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5620,7 +5593,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I12">
-    <cfRule type="containsText" dxfId="187" priority="119" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="190" priority="119" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I12))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5637,7 +5610,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I12">
-    <cfRule type="containsText" dxfId="186" priority="117" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="189" priority="117" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I12))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5654,7 +5627,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H14">
-    <cfRule type="containsText" dxfId="185" priority="115" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="188" priority="115" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H14))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5671,7 +5644,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I14">
-    <cfRule type="containsText" dxfId="184" priority="113" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="187" priority="113" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I14))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5688,7 +5661,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I14">
-    <cfRule type="containsText" dxfId="183" priority="111" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="186" priority="111" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I14))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5705,7 +5678,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J15">
-    <cfRule type="containsText" dxfId="182" priority="107" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="185" priority="107" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J15))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5722,7 +5695,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J15">
-    <cfRule type="containsText" dxfId="181" priority="105" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="184" priority="105" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J15))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5739,7 +5712,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J3:J6">
-    <cfRule type="containsText" dxfId="180" priority="41" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="183" priority="41" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5756,7 +5729,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="containsText" dxfId="179" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="182" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J7))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5773,11 +5746,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J8 J10">
-    <cfRule type="containsText" dxfId="178" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="181" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J8))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J8 J10">
+  <conditionalFormatting sqref="J10 J8">
     <cfRule type="colorScale" priority="38">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5790,11 +5763,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J9 J11">
-    <cfRule type="containsText" dxfId="177" priority="35" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="180" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J9))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J9 J11">
+  <conditionalFormatting sqref="J11 J9">
     <cfRule type="colorScale" priority="36">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5807,7 +5780,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J3:J6 J9:J11">
-    <cfRule type="containsText" dxfId="176" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="179" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5824,7 +5797,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J8">
-    <cfRule type="containsText" dxfId="175" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="178" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J8))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5841,7 +5814,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="containsText" dxfId="174" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="177" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J7))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5858,7 +5831,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I14">
-    <cfRule type="containsText" dxfId="173" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="176" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I14))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5875,7 +5848,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I14">
-    <cfRule type="containsText" dxfId="172" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="175" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I14))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5892,7 +5865,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="containsText" dxfId="171" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="174" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H13))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5909,7 +5882,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I13">
-    <cfRule type="containsText" dxfId="170" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="173" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I13))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5926,7 +5899,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I13">
-    <cfRule type="containsText" dxfId="169" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="172" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I13))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5943,7 +5916,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H14">
-    <cfRule type="containsText" dxfId="168" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="171" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H14))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5960,7 +5933,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J12">
-    <cfRule type="containsText" dxfId="167" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="170" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J12))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5977,7 +5950,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J12">
-    <cfRule type="containsText" dxfId="166" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="169" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J12))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5994,7 +5967,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J14">
-    <cfRule type="containsText" dxfId="165" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="168" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J14))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6011,7 +5984,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J14">
-    <cfRule type="containsText" dxfId="164" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="167" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J14))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6028,7 +6001,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J13">
-    <cfRule type="containsText" dxfId="163" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="166" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J13))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6045,7 +6018,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J13">
-    <cfRule type="containsText" dxfId="162" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="165" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J13))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6083,30 +6056,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="27" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="24"/>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="29"/>
-      <c r="E1" s="42" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="33" t="s">
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="34"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
       <c r="M1" s="1"/>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="27"/>
+      <c r="A2" s="28"/>
       <c r="B2" s="24" t="s">
         <v>44</v>
       </c>
@@ -6637,7 +6610,7 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="I3:I6">
-    <cfRule type="containsText" dxfId="161" priority="129" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="164" priority="129" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6654,7 +6627,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="containsText" dxfId="160" priority="127" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="163" priority="127" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I7))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6671,11 +6644,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9 I11">
-    <cfRule type="containsText" dxfId="159" priority="123" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="162" priority="123" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I9))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I9 I11">
+  <conditionalFormatting sqref="I11 I9">
     <cfRule type="colorScale" priority="124">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6688,7 +6661,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I8">
-    <cfRule type="containsText" dxfId="158" priority="121" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="161" priority="121" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I8))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6705,7 +6678,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I10">
-    <cfRule type="containsText" dxfId="157" priority="119" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="160" priority="119" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I10))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6722,7 +6695,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J3:J6">
-    <cfRule type="containsText" dxfId="156" priority="117" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="159" priority="117" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6739,7 +6712,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="containsText" dxfId="155" priority="115" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="158" priority="115" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J7))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6756,11 +6729,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J8 J10">
-    <cfRule type="containsText" dxfId="154" priority="113" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="157" priority="113" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J8))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J10 J8">
+  <conditionalFormatting sqref="J8 J10">
     <cfRule type="colorScale" priority="114">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6773,11 +6746,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J9 J11">
-    <cfRule type="containsText" dxfId="153" priority="111" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="156" priority="111" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J9))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J9 J11">
+  <conditionalFormatting sqref="J11 J9">
     <cfRule type="colorScale" priority="112">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6790,7 +6763,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J3:J6 J9:J11">
-    <cfRule type="containsText" dxfId="152" priority="109" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="155" priority="109" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6807,7 +6780,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J8">
-    <cfRule type="containsText" dxfId="151" priority="107" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="154" priority="107" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J8))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6824,7 +6797,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="containsText" dxfId="150" priority="105" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="153" priority="105" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J7))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6841,7 +6814,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I12">
-    <cfRule type="containsText" dxfId="149" priority="103" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="152" priority="103" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I12))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6858,7 +6831,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J12">
-    <cfRule type="containsText" dxfId="148" priority="101" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="151" priority="101" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J12))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6875,7 +6848,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J12">
-    <cfRule type="containsText" dxfId="147" priority="99" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="150" priority="99" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J12))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6892,7 +6865,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K3:L3 K4:K6 L4:L14">
-    <cfRule type="containsText" dxfId="146" priority="97" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="149" priority="97" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6909,7 +6882,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="containsText" dxfId="145" priority="95" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="148" priority="95" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K7))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6926,11 +6899,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K8 K10">
-    <cfRule type="containsText" dxfId="144" priority="93" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="147" priority="93" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K8))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K8 K10">
+  <conditionalFormatting sqref="K10 K8">
     <cfRule type="colorScale" priority="94">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6943,11 +6916,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K9 K11">
-    <cfRule type="containsText" dxfId="143" priority="91" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="146" priority="91" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K9))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K9 K11">
+  <conditionalFormatting sqref="K11 K9">
     <cfRule type="colorScale" priority="92">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6960,7 +6933,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K9:K11 K3:L3 K4:K6 L4:L14">
-    <cfRule type="containsText" dxfId="142" priority="89" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="145" priority="89" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6977,7 +6950,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K8">
-    <cfRule type="containsText" dxfId="141" priority="87" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="144" priority="87" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K8))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6994,7 +6967,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="containsText" dxfId="140" priority="85" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="143" priority="85" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K7))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7011,7 +6984,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="containsText" dxfId="139" priority="79" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="142" priority="79" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K12))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7028,7 +7001,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I14">
-    <cfRule type="containsText" dxfId="138" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="141" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I14))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7045,7 +7018,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I13">
-    <cfRule type="containsText" dxfId="137" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="140" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I13))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7062,7 +7035,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J13">
-    <cfRule type="containsText" dxfId="136" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="139" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J13))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7079,7 +7052,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J14">
-    <cfRule type="containsText" dxfId="135" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="138" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J14))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7096,7 +7069,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J13:J14">
-    <cfRule type="containsText" dxfId="134" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="137" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J13))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7113,7 +7086,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="containsText" dxfId="133" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="136" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K13))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7130,7 +7103,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K14">
-    <cfRule type="containsText" dxfId="132" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="135" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K14))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7147,7 +7120,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13:K14">
-    <cfRule type="containsText" dxfId="131" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="134" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K13))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7185,30 +7158,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="42" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="24"/>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="38"/>
-      <c r="E1" s="30" t="s">
+      <c r="D1" s="44"/>
+      <c r="E1" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="40"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="33" t="s">
+      <c r="F1" s="32"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="41"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="35"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="38"/>
       <c r="M1" s="1"/>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="37"/>
+      <c r="A2" s="43"/>
       <c r="B2" s="24" t="s">
         <v>44</v>
       </c>
@@ -7758,7 +7731,7 @@
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="I3:I6">
-    <cfRule type="containsText" dxfId="130" priority="115" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="133" priority="115" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7775,7 +7748,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7 I10:I11">
-    <cfRule type="containsText" dxfId="129" priority="113" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="132" priority="113" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I7))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7792,7 +7765,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I8">
-    <cfRule type="containsText" dxfId="128" priority="111" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="131" priority="111" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I8))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7809,7 +7782,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9">
-    <cfRule type="containsText" dxfId="127" priority="109" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="130" priority="109" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I9))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7826,7 +7799,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K3:L3 K4:K6 L4:L14">
-    <cfRule type="containsText" dxfId="126" priority="107" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="129" priority="107" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7843,7 +7816,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="containsText" dxfId="125" priority="105" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="128" priority="105" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K7))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7860,11 +7833,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K8 K10">
-    <cfRule type="containsText" dxfId="124" priority="103" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="127" priority="103" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K8))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K8 K10">
+  <conditionalFormatting sqref="K10 K8">
     <cfRule type="colorScale" priority="104">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -7877,11 +7850,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K9 K11">
-    <cfRule type="containsText" dxfId="123" priority="101" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="126" priority="101" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K9))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K9 K11">
+  <conditionalFormatting sqref="K11 K9">
     <cfRule type="colorScale" priority="102">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -7894,7 +7867,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K9:K11 K3:L3 K4:K6 L4:L14">
-    <cfRule type="containsText" dxfId="122" priority="99" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="125" priority="99" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7911,7 +7884,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K8">
-    <cfRule type="containsText" dxfId="121" priority="97" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="124" priority="97" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K8))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7928,7 +7901,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="containsText" dxfId="120" priority="95" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="123" priority="95" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K7))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7945,7 +7918,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I12">
-    <cfRule type="containsText" dxfId="119" priority="93" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="122" priority="93" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I12))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7962,7 +7935,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="containsText" dxfId="118" priority="91" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="121" priority="91" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K12))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7979,7 +7952,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="containsText" dxfId="117" priority="89" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="120" priority="89" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K12))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7996,7 +7969,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J3:J6">
-    <cfRule type="containsText" dxfId="116" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="119" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8013,7 +7986,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7 J10:J11">
-    <cfRule type="containsText" dxfId="115" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="118" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J7))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8030,7 +8003,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J8">
-    <cfRule type="containsText" dxfId="114" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="117" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J8))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8047,7 +8020,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J9">
-    <cfRule type="containsText" dxfId="113" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="116" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J9))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8064,7 +8037,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J12">
-    <cfRule type="containsText" dxfId="112" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="115" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J12))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8081,7 +8054,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I13">
-    <cfRule type="containsText" dxfId="111" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="114" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I13))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8098,7 +8071,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="containsText" dxfId="110" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="113" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K13))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8115,7 +8088,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="containsText" dxfId="109" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="112" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K13))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8132,7 +8105,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I14">
-    <cfRule type="containsText" dxfId="108" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="111" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I14))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8149,7 +8122,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K14">
-    <cfRule type="containsText" dxfId="107" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="110" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K14))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8166,7 +8139,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K14">
-    <cfRule type="containsText" dxfId="106" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="109" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K14))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8183,7 +8156,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J13">
-    <cfRule type="containsText" dxfId="105" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="108" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J13))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8200,7 +8173,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J14">
-    <cfRule type="containsText" dxfId="104" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="107" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J14))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8238,28 +8211,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="27" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="24"/>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="29"/>
-      <c r="E1" s="30" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="32"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="33" t="s">
+      <c r="F1" s="33"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="34"/>
-      <c r="J1" s="35"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="38"/>
       <c r="K1" s="1"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="27"/>
+      <c r="A2" s="28"/>
       <c r="B2" s="24" t="s">
         <v>44</v>
       </c>
@@ -8321,7 +8294,7 @@
         <v>0</v>
       </c>
       <c r="K3" s="23" t="str">
-        <f>IF(OR(AND(H3&gt;1,H3&lt;&gt;"-"),AND(I3&gt;1,I3&lt;&gt;"-"),AND(J3&gt;1,J3&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="K3:K15" si="0">IF(OR(AND(H3&gt;1,H3&lt;&gt;"-"),AND(I3&gt;1,I3&lt;&gt;"-"),AND(J3&gt;1,J3&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -8357,7 +8330,7 @@
         <v>0</v>
       </c>
       <c r="K4" s="23" t="str">
-        <f>IF(OR(AND(H4&gt;1,H4&lt;&gt;"-"),AND(I4&gt;1,I4&lt;&gt;"-"),AND(J4&gt;1,J4&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -8393,7 +8366,7 @@
         <v>0</v>
       </c>
       <c r="K5" s="23" t="str">
-        <f>IF(OR(AND(H5&gt;1,H5&lt;&gt;"-"),AND(I5&gt;1,I5&lt;&gt;"-"),AND(J5&gt;1,J5&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -8429,7 +8402,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="23" t="str">
-        <f>IF(OR(AND(H6&gt;1,H6&lt;&gt;"-"),AND(I6&gt;1,I6&lt;&gt;"-"),AND(J6&gt;1,J6&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -8465,7 +8438,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="23" t="str">
-        <f>IF(OR(AND(H7&gt;1,H7&lt;&gt;"-"),AND(I7&gt;1,I7&lt;&gt;"-"),AND(J7&gt;1,J7&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -8501,7 +8474,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="23" t="str">
-        <f>IF(OR(AND(H8&gt;1,H8&lt;&gt;"-"),AND(I8&gt;1,I8&lt;&gt;"-"),AND(J8&gt;1,J8&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -8537,7 +8510,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="23" t="str">
-        <f>IF(OR(AND(H9&gt;1,H9&lt;&gt;"-"),AND(I9&gt;1,I9&lt;&gt;"-"),AND(J9&gt;1,J9&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -8573,7 +8546,7 @@
         <v>0</v>
       </c>
       <c r="K10" s="23" t="str">
-        <f>IF(OR(AND(H10&gt;1,H10&lt;&gt;"-"),AND(I10&gt;1,I10&lt;&gt;"-"),AND(J10&gt;1,J10&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -8609,7 +8582,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="23" t="str">
-        <f>IF(OR(AND(H11&gt;1,H11&lt;&gt;"-"),AND(I11&gt;1,I11&lt;&gt;"-"),AND(J11&gt;1,J11&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -8645,7 +8618,7 @@
         <v>0</v>
       </c>
       <c r="K12" s="23" t="str">
-        <f>IF(OR(AND(H12&gt;1,H12&lt;&gt;"-"),AND(I12&gt;1,I12&lt;&gt;"-"),AND(J12&gt;1,J12&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -8681,7 +8654,7 @@
         <v>0</v>
       </c>
       <c r="K13" s="23" t="str">
-        <f>IF(OR(AND(H13&gt;1,H13&lt;&gt;"-"),AND(I13&gt;1,I13&lt;&gt;"-"),AND(J13&gt;1,J13&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -8717,13 +8690,13 @@
         <v>0</v>
       </c>
       <c r="K14" s="23" t="str">
-        <f>IF(OR(AND(H14&gt;1,H14&lt;&gt;"-"),AND(I14&gt;1,I14&lt;&gt;"-"),AND(J14&gt;1,J14&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="K15" s="23" t="str">
-        <f>IF(OR(AND(H15&gt;1,H15&lt;&gt;"-"),AND(I15&gt;1,I15&lt;&gt;"-"),AND(J15&gt;1,J15&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -8737,7 +8710,7 @@
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="H3:H6">
-    <cfRule type="containsText" dxfId="103" priority="103" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="106" priority="103" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8754,7 +8727,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H7 H10:H11">
-    <cfRule type="containsText" dxfId="102" priority="101" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="105" priority="101" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H7))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8771,7 +8744,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H8">
-    <cfRule type="containsText" dxfId="101" priority="99" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="104" priority="99" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H8))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8788,7 +8761,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H9">
-    <cfRule type="containsText" dxfId="100" priority="97" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="103" priority="97" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H9))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8805,7 +8778,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I3:J3 I4:I6 J4:J12">
-    <cfRule type="containsText" dxfId="99" priority="95" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="102" priority="95" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8822,7 +8795,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="containsText" dxfId="98" priority="93" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="101" priority="93" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I7))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8839,11 +8812,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I8 I10">
-    <cfRule type="containsText" dxfId="97" priority="91" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="100" priority="91" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I8))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I8 I10">
+  <conditionalFormatting sqref="I10 I8">
     <cfRule type="colorScale" priority="92">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -8856,11 +8829,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9 I11">
-    <cfRule type="containsText" dxfId="96" priority="89" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="99" priority="89" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I9))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I9 I11">
+  <conditionalFormatting sqref="I11 I9">
     <cfRule type="colorScale" priority="90">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -8873,7 +8846,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9:I11 I3:J3 I4:I6 J4:J12">
-    <cfRule type="containsText" dxfId="95" priority="87" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="98" priority="87" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8890,7 +8863,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I8">
-    <cfRule type="containsText" dxfId="94" priority="85" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="97" priority="85" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I8))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8907,7 +8880,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="containsText" dxfId="93" priority="83" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="96" priority="83" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I7))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8924,7 +8897,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="containsText" dxfId="92" priority="81" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="95" priority="81" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H12))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8941,7 +8914,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I12">
-    <cfRule type="containsText" dxfId="91" priority="79" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="94" priority="79" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I12))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8958,7 +8931,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I12">
-    <cfRule type="containsText" dxfId="90" priority="77" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="93" priority="77" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I12))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8975,7 +8948,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="containsText" dxfId="89" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="92" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H13))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8992,7 +8965,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J13:J14">
-    <cfRule type="containsText" dxfId="88" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="91" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J13))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9009,7 +8982,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I13">
-    <cfRule type="containsText" dxfId="87" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="90" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I13))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9026,7 +8999,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I13 J13:J14">
-    <cfRule type="containsText" dxfId="86" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="89" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I13))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9043,7 +9016,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H14">
-    <cfRule type="containsText" dxfId="85" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="88" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H14))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9060,7 +9033,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I14">
-    <cfRule type="containsText" dxfId="84" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="87" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I14))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9077,7 +9050,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I14">
-    <cfRule type="containsText" dxfId="83" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="86" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I14))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9115,28 +9088,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="27" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="24"/>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="29"/>
-      <c r="E1" s="30" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="32"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="33" t="s">
+      <c r="F1" s="33"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="34"/>
-      <c r="J1" s="35"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="38"/>
       <c r="K1" s="1"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="27"/>
+      <c r="A2" s="28"/>
       <c r="B2" s="25" t="s">
         <v>44</v>
       </c>
@@ -9600,7 +9573,7 @@
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="H3:H6">
-    <cfRule type="containsText" dxfId="82" priority="101" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="85" priority="101" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9617,7 +9590,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H7 H10:H11">
-    <cfRule type="containsText" dxfId="81" priority="99" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="84" priority="99" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H7))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9634,7 +9607,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H8">
-    <cfRule type="containsText" dxfId="80" priority="97" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="83" priority="97" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H8))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9651,7 +9624,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H9">
-    <cfRule type="containsText" dxfId="79" priority="95" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="82" priority="95" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H9))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9668,7 +9641,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I3:J3 I4:I6 J4:J14">
-    <cfRule type="containsText" dxfId="78" priority="93" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="81" priority="93" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9685,7 +9658,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="containsText" dxfId="77" priority="91" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="80" priority="91" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I7))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9702,11 +9675,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I8 I10">
-    <cfRule type="containsText" dxfId="76" priority="89" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="79" priority="89" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I8))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I8 I10">
+  <conditionalFormatting sqref="I10 I8">
     <cfRule type="colorScale" priority="90">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -9719,11 +9692,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9 I11">
-    <cfRule type="containsText" dxfId="75" priority="87" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="78" priority="87" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I9))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I9 I11">
+  <conditionalFormatting sqref="I11 I9">
     <cfRule type="colorScale" priority="88">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -9736,7 +9709,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9:I11 I3:J3 I4:I6 J4:J14">
-    <cfRule type="containsText" dxfId="74" priority="85" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="77" priority="85" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9753,7 +9726,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I8">
-    <cfRule type="containsText" dxfId="73" priority="83" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="76" priority="83" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I8))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9770,7 +9743,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="containsText" dxfId="72" priority="81" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="75" priority="81" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I7))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9787,7 +9760,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="containsText" dxfId="71" priority="79" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="74" priority="79" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H12))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9804,7 +9777,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I12">
-    <cfRule type="containsText" dxfId="70" priority="77" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="73" priority="77" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I12))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9821,7 +9794,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I12">
-    <cfRule type="containsText" dxfId="69" priority="75" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="72" priority="75" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I12))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9838,7 +9811,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="containsText" dxfId="68" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="71" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H13))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9855,7 +9828,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I13">
-    <cfRule type="containsText" dxfId="67" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="70" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I13))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9872,7 +9845,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I13">
-    <cfRule type="containsText" dxfId="66" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="69" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I13))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9889,7 +9862,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H14">
-    <cfRule type="containsText" dxfId="65" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="68" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H14))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9906,7 +9879,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I14">
-    <cfRule type="containsText" dxfId="64" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="67" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I14))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9923,7 +9896,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I14">
-    <cfRule type="containsText" dxfId="63" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="66" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I14))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9961,30 +9934,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="27" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="24"/>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="29"/>
-      <c r="E1" s="30" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="40"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="33" t="s">
+      <c r="F1" s="32"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="41"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="35"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="38"/>
       <c r="M1" s="1"/>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="27"/>
+      <c r="A2" s="28"/>
       <c r="B2" s="24" t="s">
         <v>44</v>
       </c>
@@ -10058,7 +10031,7 @@
         <v>0</v>
       </c>
       <c r="M3" s="23" t="str">
-        <f>IF(OR(AND(I3&gt;1,I3&lt;&gt;"-"),AND(J3&gt;1,J3&lt;&gt;"-"),AND(K3&gt;1,K3&lt;&gt;"-"),AND(L3&gt;1,L3&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="M3:M14" si="0">IF(OR(AND(I3&gt;1,I3&lt;&gt;"-"),AND(J3&gt;1,J3&lt;&gt;"-"),AND(K3&gt;1,K3&lt;&gt;"-"),AND(L3&gt;1,L3&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -10100,7 +10073,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="23" t="str">
-        <f>IF(OR(AND(I4&gt;1,I4&lt;&gt;"-"),AND(J4&gt;1,J4&lt;&gt;"-"),AND(K4&gt;1,K4&lt;&gt;"-"),AND(L4&gt;1,L4&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -10142,7 +10115,7 @@
         <v>0</v>
       </c>
       <c r="M5" s="23" t="str">
-        <f>IF(OR(AND(I5&gt;1,I5&lt;&gt;"-"),AND(J5&gt;1,J5&lt;&gt;"-"),AND(K5&gt;1,K5&lt;&gt;"-"),AND(L5&gt;1,L5&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -10184,7 +10157,7 @@
         <v>0</v>
       </c>
       <c r="M6" s="23" t="str">
-        <f>IF(OR(AND(I6&gt;1,I6&lt;&gt;"-"),AND(J6&gt;1,J6&lt;&gt;"-"),AND(K6&gt;1,K6&lt;&gt;"-"),AND(L6&gt;1,L6&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -10226,7 +10199,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="23" t="str">
-        <f>IF(OR(AND(I7&gt;1,I7&lt;&gt;"-"),AND(J7&gt;1,J7&lt;&gt;"-"),AND(K7&gt;1,K7&lt;&gt;"-"),AND(L7&gt;1,L7&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -10268,7 +10241,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="23" t="str">
-        <f>IF(OR(AND(I8&gt;1,I8&lt;&gt;"-"),AND(J8&gt;1,J8&lt;&gt;"-"),AND(K8&gt;1,K8&lt;&gt;"-"),AND(L8&gt;1,L8&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -10310,7 +10283,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="23" t="str">
-        <f>IF(OR(AND(I9&gt;1,I9&lt;&gt;"-"),AND(J9&gt;1,J9&lt;&gt;"-"),AND(K9&gt;1,K9&lt;&gt;"-"),AND(L9&gt;1,L9&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -10352,7 +10325,7 @@
         <v>0</v>
       </c>
       <c r="M10" s="23" t="str">
-        <f>IF(OR(AND(I10&gt;1,I10&lt;&gt;"-"),AND(J10&gt;1,J10&lt;&gt;"-"),AND(K10&gt;1,K10&lt;&gt;"-"),AND(L10&gt;1,L10&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -10394,7 +10367,7 @@
         <v>0</v>
       </c>
       <c r="M11" s="23" t="str">
-        <f>IF(OR(AND(I11&gt;1,I11&lt;&gt;"-"),AND(J11&gt;1,J11&lt;&gt;"-"),AND(K11&gt;1,K11&lt;&gt;"-"),AND(L11&gt;1,L11&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -10436,7 +10409,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="23" t="str">
-        <f>IF(OR(AND(I12&gt;1,I12&lt;&gt;"-"),AND(J12&gt;1,J12&lt;&gt;"-"),AND(K12&gt;1,K12&lt;&gt;"-"),AND(L12&gt;1,L12&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -10478,7 +10451,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="23" t="str">
-        <f>IF(OR(AND(I13&gt;1,I13&lt;&gt;"-"),AND(J13&gt;1,J13&lt;&gt;"-"),AND(K13&gt;1,K13&lt;&gt;"-"),AND(L13&gt;1,L13&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -10520,7 +10493,7 @@
         <v>0</v>
       </c>
       <c r="M14" s="23" t="str">
-        <f>IF(OR(AND(I14&gt;1,I14&lt;&gt;"-"),AND(J14&gt;1,J14&lt;&gt;"-"),AND(K14&gt;1,K14&lt;&gt;"-"),AND(L14&gt;1,L14&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -10534,7 +10507,7 @@
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="I3:I4 I6">
-    <cfRule type="containsText" dxfId="62" priority="159" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="65" priority="159" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10551,7 +10524,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7 I10:I11">
-    <cfRule type="containsText" dxfId="61" priority="157" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="64" priority="157" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I7))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10568,7 +10541,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I8">
-    <cfRule type="containsText" dxfId="60" priority="155" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="63" priority="155" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I8))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10585,7 +10558,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9">
-    <cfRule type="containsText" dxfId="59" priority="153" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="62" priority="153" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I9))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10602,7 +10575,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K3:K4 K6">
-    <cfRule type="containsText" dxfId="58" priority="151" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="61" priority="151" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10619,7 +10592,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="containsText" dxfId="57" priority="149" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="60" priority="149" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K7))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10636,11 +10609,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K8 K10">
-    <cfRule type="containsText" dxfId="56" priority="147" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="59" priority="147" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K8))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K10 K8">
+  <conditionalFormatting sqref="K8 K10">
     <cfRule type="colorScale" priority="148">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -10653,11 +10626,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K9 K11">
-    <cfRule type="containsText" dxfId="55" priority="145" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="58" priority="145" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K9))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K9 K11">
+  <conditionalFormatting sqref="K11 K9">
     <cfRule type="colorScale" priority="146">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -10670,7 +10643,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K3:K4 K9:K11 K6">
-    <cfRule type="containsText" dxfId="54" priority="143" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="57" priority="143" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10687,7 +10660,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K8">
-    <cfRule type="containsText" dxfId="53" priority="141" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="56" priority="141" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K8))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10704,7 +10677,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="containsText" dxfId="52" priority="139" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="55" priority="139" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K7))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10721,7 +10694,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I12">
-    <cfRule type="containsText" dxfId="51" priority="137" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="54" priority="137" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I12))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10738,7 +10711,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="containsText" dxfId="50" priority="135" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="53" priority="135" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K12))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10755,7 +10728,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="containsText" dxfId="49" priority="133" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="52" priority="133" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K12))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10772,7 +10745,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J3:J6">
-    <cfRule type="containsText" dxfId="48" priority="69" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="51" priority="69" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10789,7 +10762,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="containsText" dxfId="47" priority="67" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="50" priority="67" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J7))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10806,11 +10779,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J8 J10">
-    <cfRule type="containsText" dxfId="46" priority="65" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="49" priority="65" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J8))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J8 J10">
+  <conditionalFormatting sqref="J10 J8">
     <cfRule type="colorScale" priority="66">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -10823,11 +10796,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J9 J11">
-    <cfRule type="containsText" dxfId="45" priority="63" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="48" priority="63" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J9))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J9 J11">
+  <conditionalFormatting sqref="J11 J9">
     <cfRule type="colorScale" priority="64">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -10840,7 +10813,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J3:J6 J9:J11">
-    <cfRule type="containsText" dxfId="44" priority="61" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="47" priority="61" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10857,7 +10830,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J8">
-    <cfRule type="containsText" dxfId="43" priority="59" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="46" priority="59" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J8))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10874,7 +10847,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="containsText" dxfId="42" priority="57" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="45" priority="57" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J7))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10891,7 +10864,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J12">
-    <cfRule type="containsText" dxfId="41" priority="55" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="44" priority="55" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J12))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10908,7 +10881,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J12">
-    <cfRule type="containsText" dxfId="40" priority="53" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="43" priority="53" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J12))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10925,7 +10898,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L3:L6">
-    <cfRule type="containsText" dxfId="39" priority="51" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="42" priority="51" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10942,7 +10915,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L7">
-    <cfRule type="containsText" dxfId="38" priority="49" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="41" priority="49" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L7))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10959,11 +10932,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L8 L10">
-    <cfRule type="containsText" dxfId="37" priority="47" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="40" priority="47" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L8))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L10 L8">
+  <conditionalFormatting sqref="L8 L10">
     <cfRule type="colorScale" priority="48">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -10976,11 +10949,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L9 L11">
-    <cfRule type="containsText" dxfId="36" priority="45" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="39" priority="45" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L9))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L11 L9">
+  <conditionalFormatting sqref="L9 L11">
     <cfRule type="colorScale" priority="46">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -10993,7 +10966,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L3:L6 L9:L11">
-    <cfRule type="containsText" dxfId="35" priority="43" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="38" priority="43" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11010,7 +10983,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L8">
-    <cfRule type="containsText" dxfId="34" priority="41" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="37" priority="41" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L8))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11027,7 +11000,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L7">
-    <cfRule type="containsText" dxfId="33" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="36" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L7))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11044,7 +11017,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L12">
-    <cfRule type="containsText" dxfId="32" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="35" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L12))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11061,7 +11034,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L12">
-    <cfRule type="containsText" dxfId="31" priority="35" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="34" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L12))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11078,7 +11051,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5">
-    <cfRule type="containsText" dxfId="30" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="33" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K5))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11095,7 +11068,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5">
-    <cfRule type="containsText" dxfId="29" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="32" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I5))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11112,7 +11085,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5">
-    <cfRule type="containsText" dxfId="28" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="31" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I5))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11129,7 +11102,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I13">
-    <cfRule type="containsText" dxfId="27" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="30" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I13))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11146,7 +11119,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="containsText" dxfId="26" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="29" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K13))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11163,7 +11136,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="containsText" dxfId="25" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="28" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K13))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11180,7 +11153,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I14">
-    <cfRule type="containsText" dxfId="24" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="27" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I14))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11197,7 +11170,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K14">
-    <cfRule type="containsText" dxfId="23" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="26" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K14))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11214,7 +11187,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K14">
-    <cfRule type="containsText" dxfId="22" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="25" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K14))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11231,7 +11204,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J13">
-    <cfRule type="containsText" dxfId="21" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="24" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J13))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11248,7 +11221,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J13">
-    <cfRule type="containsText" dxfId="20" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="23" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J13))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11265,7 +11238,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J14">
-    <cfRule type="containsText" dxfId="19" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="22" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J14))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11282,7 +11255,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J14">
-    <cfRule type="containsText" dxfId="18" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="21" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J14))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11299,7 +11272,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L13">
-    <cfRule type="containsText" dxfId="17" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="20" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L13))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11316,7 +11289,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L13">
-    <cfRule type="containsText" dxfId="16" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="19" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L13))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11333,7 +11306,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L14">
-    <cfRule type="containsText" dxfId="15" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="18" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L14))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11350,7 +11323,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L14">
-    <cfRule type="containsText" dxfId="14" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="17" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L14))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11388,20 +11361,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="27" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="24"/>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="29"/>
-      <c r="E1" s="28" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="29" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="45"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="33" t="s">
+      <c r="G1" s="30"/>
+      <c r="H1" s="35" t="s">
         <v>10</v>
       </c>
       <c r="I1" s="46"/>
@@ -11409,7 +11382,7 @@
       <c r="K1" s="1"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="27"/>
+      <c r="A2" s="28"/>
       <c r="B2" s="24" t="s">
         <v>44</v>
       </c>
@@ -11881,7 +11854,7 @@
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="H3:J3 H4:I6 J4:J12">
-    <cfRule type="containsText" dxfId="13" priority="101" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="16" priority="101" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11898,7 +11871,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H7:I7">
-    <cfRule type="containsText" dxfId="12" priority="99" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="15" priority="99" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H7))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11915,7 +11888,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H8:I8 H10:I10">
-    <cfRule type="containsText" dxfId="11" priority="97" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="14" priority="97" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H8))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11932,7 +11905,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H9:I9 H11:I11">
-    <cfRule type="containsText" dxfId="10" priority="95" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="13" priority="95" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H9))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11949,7 +11922,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9:I11 I3:J3 I4:I6 J4:J12">
-    <cfRule type="containsText" dxfId="9" priority="93" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="12" priority="93" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11966,7 +11939,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I8">
-    <cfRule type="containsText" dxfId="8" priority="79" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="11" priority="79" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I8))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11983,7 +11956,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="containsText" dxfId="7" priority="77" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="10" priority="77" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I7))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12000,7 +11973,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12:I12">
-    <cfRule type="containsText" dxfId="6" priority="75" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="9" priority="75" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H12))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12017,7 +11990,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I12">
-    <cfRule type="containsText" dxfId="5" priority="73" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="8" priority="73" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I12))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12034,7 +12007,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J13:J14">
-    <cfRule type="containsText" dxfId="4" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="7" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J13))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12051,7 +12024,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13:I13">
-    <cfRule type="containsText" dxfId="3" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H13))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12068,7 +12041,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I13 J13:J14">
-    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I13))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12085,7 +12058,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H14:I14">
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H14))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12102,7 +12075,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I14">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I14))))</formula>
     </cfRule>
   </conditionalFormatting>
